--- a/files/閃令令商品进货表.xlsx
+++ b/files/閃令令商品进货表.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\React-Project\SLL-tools\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\React-Project\SLL-tools\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9285D8D2-C7A7-484D-93EC-4FA9DBDF39B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB42C96B-98BA-4DD4-8C41-1BF39895F5CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="15552" windowHeight="16656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="2" r:id="rId1"/>
+    <sheet name="进货表" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -731,10 +731,6 @@
     <t>Nike耐克黑白板鞋CourtVision1低帮可回收材料经典耐磨DH2987-001</t>
   </si>
   <si>
-    <t>商品</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>Adidas阿迪达斯 Neo Entrap合成革 简约低帮板鞋FZ1119/JQ5047</t>
   </si>
   <si>
@@ -774,6 +770,10 @@
   </si>
   <si>
     <t>Adidas阿迪达斯 YEEZY500StoneSalt灰色老爹鞋低帮耐磨透气IE4783</t>
+  </si>
+  <si>
+    <t>拼多多商品名</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1493,7 +1493,7 @@
     <col min="1" max="1" width="9.453125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.453125" style="2" customWidth="1"/>
     <col min="3" max="3" width="14.6328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="31" style="3" customWidth="1"/>
+    <col min="4" max="4" width="57.7265625" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.36328125" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.36328125" style="2" customWidth="1"/>
     <col min="7" max="7" width="12.90625" style="4" customWidth="1"/>
@@ -1515,7 +1515,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>3</v>
@@ -1631,7 +1631,7 @@
         <v>21</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="8">
@@ -1784,7 +1784,7 @@
         <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="8">
@@ -1892,7 +1892,7 @@
         <v>45</v>
       </c>
       <c r="D17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E17" s="11"/>
       <c r="F17" s="11">
@@ -1916,7 +1916,7 @@
         <v>47</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E18" s="11"/>
       <c r="F18" s="11">
@@ -1929,7 +1929,7 @@
         <v>46039</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="30" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>15</v>
       </c>
@@ -1940,7 +1940,7 @@
         <v>49</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2">
@@ -1988,7 +1988,7 @@
         <v>54</v>
       </c>
       <c r="D21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E21" s="11"/>
       <c r="F21" s="11">
@@ -2099,7 +2099,7 @@
         <v>46035</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="30" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>10</v>
       </c>
@@ -2110,7 +2110,7 @@
         <v>68</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2">
@@ -2157,7 +2157,7 @@
         <v>72</v>
       </c>
       <c r="D28" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F28" s="2">
         <v>679.6</v>
@@ -2231,7 +2231,7 @@
         <v>79</v>
       </c>
       <c r="D31" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E31" s="1" t="e" vm="1">
         <f ca="1">_xlfn.DISPIMG("ID_704A651B69234A6FB29D2AB4CCF73F6D",1)</f>
@@ -2247,7 +2247,7 @@
         <v>46059</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="30" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>10</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>46059</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="30" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="18" t="s">
         <v>117</v>
       </c>
@@ -2307,7 +2307,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="30" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="18" t="s">
         <v>117</v>
       </c>
@@ -2340,7 +2340,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="30" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="18" t="s">
         <v>117</v>
       </c>
@@ -2505,7 +2505,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="30" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" s="18" t="s">
         <v>117</v>
       </c>
@@ -2596,10 +2596,10 @@
         <v>118</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D43" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F43" s="2">
         <v>74</v>
@@ -2610,10 +2610,10 @@
         <v>118</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D44" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F44" s="2">
         <v>144</v>
@@ -2628,12 +2628,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<pixelators xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <pixelatorList sheetStid="2"/>
-</pixelators>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <woProps xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <woSheetsProps>
     <woSheetProps sheetStid="2" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0" isDbDashBoardSheet="0" isFlexPaperSheet="0" topPadding="30" bottomPadding="30" leftPadding="15" rightPadding="15">
@@ -2647,8 +2641,14 @@
 </woProps>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<pixelators xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <pixelatorList sheetStid="2"/>
+</pixelators>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{224D003E-15C9-4FFE-AB16-9E66474EAE4E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06C82605-B75B-4693-9329-32AAD527C692}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
@@ -2657,7 +2657,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06C82605-B75B-4693-9329-32AAD527C692}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{224D003E-15C9-4FFE-AB16-9E66474EAE4E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
